--- a/public/post/drafts/season-prediction/ladies_simple-model-tests-predicted_mae.xlsx
+++ b/public/post/drafts/season-prediction/ladies_simple-model-tests-predicted_mae.xlsx
@@ -610,25 +610,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.156791468031921</v>
+        <v>0.155454683440822</v>
       </c>
       <c r="C9" t="n">
-        <v>0.170733030812844</v>
+        <v>0.166378332981065</v>
       </c>
       <c r="D9" t="n">
-        <v>0.166807381553309</v>
+        <v>0.133888108921903</v>
       </c>
       <c r="E9" t="n">
-        <v>0.199846501740125</v>
+        <v>0.205216438061272</v>
       </c>
       <c r="F9" t="n">
-        <v>0.137196427366047</v>
+        <v>0.139829252512377</v>
       </c>
       <c r="G9" t="n">
-        <v>0.169499658089918</v>
+        <v>0.172235313498335</v>
       </c>
       <c r="H9" t="n">
-        <v>0.166812411265694</v>
+        <v>0.162167021569295</v>
       </c>
     </row>
     <row r="10">
